--- a/output/pdf_financials_xlsx/KXS.xlsx
+++ b/output/pdf_financials_xlsx/KXS.xlsx
@@ -4803,7 +4803,7 @@
         <v>-0.519</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.284</v>
+        <v>-0.676</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>-0.319</v>

--- a/output/pdf_financials_xlsx/KXS.xlsx
+++ b/output/pdf_financials_xlsx/KXS.xlsx
@@ -1773,19 +1773,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>1.151</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>1.726</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>2.494</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>3.618</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>9.272</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -5197,37 +5197,37 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.151</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.726</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>2.494</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>3.618</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>9.272</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.227</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.245</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>3.564</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>5.404</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>5.314</v>
       </c>
       <c r="M100" s="1" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -25046,7 +25046,11 @@
           <t>Depreciation of property and equipment (note 16)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -25572,7 +25576,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -26102,7 +26110,11 @@
           <t>Depreciation of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>1.151</v>
       </c>
